--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484596_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484596_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.7952</v>
+        <v>11.3966</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2346</v>
+        <v>5.9846</v>
       </c>
       <c r="F2" t="n">
-        <v>5.5606</v>
+        <v>5.412</v>
       </c>
       <c r="G2" t="n">
         <v>5.5122</v>
@@ -610,13 +610,13 @@
         <v>3.1154</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8511</v>
+        <v>1.4525</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8846</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9665</v>
+        <v>0.8178</v>
       </c>
       <c r="V2" t="n">
         <v>2.2328</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.982699999999999</v>
+        <v>9.9839</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4085</v>
+        <v>5.1777</v>
       </c>
       <c r="F3" t="n">
-        <v>5.5742</v>
+        <v>4.8063</v>
       </c>
       <c r="G3" t="n">
         <v>3.8712</v>
@@ -688,13 +688,13 @@
         <v>3.2986</v>
       </c>
       <c r="S3" t="n">
-        <v>0.902</v>
+        <v>0.9033</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6244</v>
+        <v>0.1448</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5264</v>
+        <v>0.7585</v>
       </c>
       <c r="V3" t="n">
         <v>1.9109</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.2281</v>
+        <v>8.0557</v>
       </c>
       <c r="E4" t="n">
-        <v>3.721</v>
+        <v>4.2018</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5071</v>
+        <v>3.8539</v>
       </c>
       <c r="G4" t="n">
         <v>5.1832</v>
@@ -766,13 +766,13 @@
         <v>2.7489</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7039</v>
+        <v>0.1237</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6244</v>
+        <v>-0.1436</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0795</v>
+        <v>0.2673</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.6191</v>
+        <v>3.7836</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5429</v>
+        <v>1.9799</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0762</v>
+        <v>1.8037</v>
       </c>
       <c r="G5" t="n">
         <v>2.6296</v>
@@ -844,13 +844,13 @@
         <v>2.0158</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6072</v>
+        <v>-0.2283</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5664</v>
+        <v>0.0034</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0408</v>
+        <v>-0.2317</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6335</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. MONTANO LINARES</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1916</v>
+        <v>3.619</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8652</v>
+        <v>-0.4533</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0568</v>
+        <v>4.0723</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.185</v>
+        <v>3.9427</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5778</v>
+        <v>2.8878</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7629</v>
+        <v>1.0549</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.0227</v>
+        <v>2.6715</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7337</v>
+        <v>2.6101</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.7564</v>
+        <v>0.0614</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8377</v>
+        <v>1.2712</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1558</v>
+        <v>0.2777</v>
       </c>
       <c r="O6" t="n">
         <v>0.9935</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4661</v>
+        <v>0.733</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2986</v>
+        <v>2.5656</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6332</v>
+        <v>-0.1325</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7127</v>
+        <v>-0.368</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0795</v>
+        <v>0.2355</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2774</v>
+        <v>-0.9242</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2774</v>
+        <v>-0.9242</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>P. ROCATI ALEGRE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.16</v>
+        <v>3.3541</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8379</v>
+        <v>0.7922</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9979</v>
+        <v>2.5619</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9427</v>
+        <v>2.7401</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8878</v>
+        <v>1.3489</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0549</v>
+        <v>1.3912</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6715</v>
+        <v>2.2549</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6101</v>
+        <v>1.5047</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0614</v>
+        <v>0.7501</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2712</v>
+        <v>0.4852</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2777</v>
+        <v>-0.1558</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9935</v>
+        <v>0.641</v>
       </c>
       <c r="P7" t="n">
-        <v>0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5656</v>
+        <v>2.1991</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5915</v>
+        <v>0.2475</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7526</v>
+        <v>0.3699</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1611</v>
+        <v>-0.1224</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9242</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9242</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ROCATI ALEGRE</t>
+          <t>K. MONTANO LINARES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.9249</v>
+        <v>3.2089</v>
       </c>
       <c r="E8" t="n">
-        <v>0.586</v>
+        <v>-1.1948</v>
       </c>
       <c r="F8" t="n">
-        <v>2.339</v>
+        <v>4.4037</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7401</v>
+        <v>-0.185</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3489</v>
+        <v>0.5778</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3912</v>
+        <v>-0.7629</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2549</v>
+        <v>-1.0227</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5047</v>
+        <v>0.7337</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7501</v>
+        <v>-1.7564</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4852</v>
+        <v>0.8377</v>
       </c>
       <c r="N8" t="n">
         <v>-0.1558</v>
       </c>
       <c r="O8" t="n">
-        <v>0.641</v>
+        <v>0.9935</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3665</v>
+        <v>1.4661</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1991</v>
+        <v>3.2986</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1817</v>
+        <v>0.6505</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1637</v>
+        <v>0.3831</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3453</v>
+        <v>0.2673</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.2774</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2774</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7662</v>
+        <v>-0.5709</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0948</v>
+        <v>-0.9987</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3287</v>
+        <v>0.4277</v>
       </c>
       <c r="G11" t="n">
         <v>0.3774</v>
@@ -1312,13 +1312,13 @@
         <v>0.1833</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4106</v>
+        <v>-0.2153</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2202</v>
+        <v>-0.1241</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1903</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8551</v>
+        <v>-0.7752</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4259</v>
+        <v>-3.3708</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5708</v>
+        <v>2.5956</v>
       </c>
       <c r="G12" t="n">
         <v>-2.361</v>
@@ -1390,13 +1390,13 @@
         <v>1.8326</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1117</v>
+        <v>-0.0319</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0905</v>
+        <v>0.1456</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2022</v>
+        <v>-0.1774</v>
       </c>
       <c r="V12" t="n">
         <v>2.5339</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3594</v>
+        <v>-0.8618</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4911</v>
+        <v>-3.0925</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1317</v>
+        <v>2.2307</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3448</v>
@@ -1468,13 +1468,13 @@
         <v>2.0158</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1979</v>
+        <v>-0.7002</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6606</v>
+        <v>-0.2621</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5373</v>
+        <v>-0.4382</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.5433</v>
+        <v>-2.2657</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.196</v>
+        <v>-0.8935</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3474</v>
+        <v>-1.3722</v>
       </c>
       <c r="G14" t="n">
         <v>1.4648</v>
@@ -1546,13 +1546,13 @@
         <v>1.4661</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7857</v>
+        <v>-0.5081</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5505</v>
+        <v>-0.2481</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2352</v>
+        <v>-0.26</v>
       </c>
       <c r="V14" t="n">
         <v>-2.8559</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>40.60320000000001</v>
+        <v>41.1538</v>
       </c>
       <c r="E15" t="n">
-        <v>9.807700000000001</v>
+        <v>10.3582</v>
       </c>
       <c r="F15" t="n">
         <v>30.79560000000001</v>
@@ -1624,13 +1624,13 @@
         <v>24.7398</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0105</v>
+        <v>1.5612</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.01479999999999959</v>
+        <v>0.5355000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0255</v>
+        <v>1.0254</v>
       </c>
       <c r="V15" t="n">
         <v>3.5414</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MONFORTE MARTINEZ</t>
+          <t>L. JURADO TRAVER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4672</v>
+        <v>2.9545</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7703</v>
+        <v>3.6293</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6969</v>
+        <v>-0.6748</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5653</v>
+        <v>0.1438</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8603</v>
+        <v>-0.2186</v>
       </c>
       <c r="I16" t="n">
-        <v>0.705</v>
+        <v>0.3623</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4801</v>
+        <v>1.8397</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4801</v>
+        <v>1.8298</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.0098</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0852</v>
+        <v>-1.6959</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6198</v>
+        <v>-2.0484</v>
       </c>
       <c r="O16" t="n">
-        <v>0.705</v>
+        <v>0.3525</v>
       </c>
       <c r="P16" t="n">
-        <v>0.733</v>
+        <v>1.2828</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3809</v>
+        <v>-0.6736</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8296</v>
+        <v>-0.1108</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5513</v>
+        <v>-0.5628</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.212</v>
+        <v>2.2016</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6231</v>
+        <v>1.9005</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5889</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. JURADO TRAVER</t>
+          <t>J. MONFORTE MARTINEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1896</v>
+        <v>2.3133</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2447</v>
+        <v>1.6164</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0551</v>
+        <v>0.6969</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1438</v>
+        <v>2.5653</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2186</v>
+        <v>1.8603</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3623</v>
+        <v>0.705</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8397</v>
+        <v>2.4801</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8298</v>
+        <v>2.4801</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0098</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6959</v>
+        <v>0.0852</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0484</v>
+        <v>-0.6198</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3525</v>
+        <v>0.705</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4385</v>
+        <v>1.227</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4955</v>
+        <v>0.6757</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9431</v>
+        <v>0.5513</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2016</v>
+        <v>-2.212</v>
       </c>
       <c r="W17" t="n">
-        <v>1.9005</v>
+        <v>-0.6231</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3011</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="18">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.028</v>
+        <v>-1.91</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.282</v>
+        <v>-2.0897</v>
       </c>
       <c r="F20" t="n">
-        <v>0.254</v>
+        <v>0.1797</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0886</v>
@@ -2014,13 +2014,13 @@
         <v>0.5498</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2509</v>
+        <v>-0.1329</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4955</v>
+        <v>-0.3032</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2446</v>
+        <v>0.1702</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3219</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. VANOUKIA</t>
+          <t>F. ROMAN MORA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3568</v>
+        <v>-2.8745</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4499</v>
+        <v>-3.6808</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0931</v>
+        <v>0.8063</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0901</v>
+        <v>-1.937</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1605</v>
+        <v>-1.7446</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9296</v>
+        <v>-0.1925</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5359</v>
+        <v>-1.8147</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1051</v>
+        <v>-1.1737</v>
       </c>
       <c r="L21" t="n">
         <v>-0.641</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5541</v>
+        <v>-0.1223</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2656</v>
+        <v>-0.5709</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2885</v>
+        <v>0.4486</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.1991</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7489</v>
+        <v>-2.0158</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5498</v>
+        <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.2562</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1652</v>
+        <v>0.1497</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0975</v>
+        <v>0.1065</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. ROMAN MORA</t>
+          <t>M. VANOUKIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5287</v>
+        <v>-3.335</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1616</v>
+        <v>-3.3538</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6329</v>
+        <v>0.0188</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.937</v>
+        <v>-1.0901</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7446</v>
+        <v>-0.1605</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1925</v>
+        <v>-0.9296</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8147</v>
+        <v>-0.5359</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1737</v>
+        <v>0.1051</v>
       </c>
       <c r="L22" t="n">
         <v>-0.641</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1223</v>
+        <v>-0.5541</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5709</v>
+        <v>-0.2656</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4486</v>
+        <v>-0.2885</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5498</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0158</v>
+        <v>-2.7489</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4661</v>
+        <v>0.5498</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.398</v>
+        <v>-0.0458</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3311</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0669</v>
+        <v>0.0232</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.234</v>
+        <v>-3.9819</v>
       </c>
       <c r="E23" t="n">
         <v>-1.3966</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8374</v>
+        <v>-2.5853</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5171</v>
@@ -2248,13 +2248,13 @@
         <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0449</v>
+        <v>0.297</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1855</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2304</v>
+        <v>0.4824</v>
       </c>
       <c r="V23" t="n">
         <v>-2.212</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. MICHAEL KING</t>
+          <t>D. CHALATASHVILI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6816</v>
+        <v>-4.7356</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.0422</v>
+        <v>-5.3573</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6394</v>
+        <v>0.6216</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.1679</v>
+        <v>-4.0513</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.53</v>
+        <v>-2.4165</v>
       </c>
       <c r="I24" t="n">
-        <v>0.362</v>
+        <v>-1.6348</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3025</v>
+        <v>-3.326</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3441</v>
+        <v>-1.4029</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0417</v>
+        <v>-1.9231</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8655</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.1858</v>
+        <v>-1.0136</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3204</v>
+        <v>0.2882</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.3823</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R24" t="n">
         <v>1.2828</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1314</v>
+        <v>0.1874</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0746</v>
+        <v>-0.1987</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0567</v>
+        <v>0.3861</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDES</t>
+          <t>D. MICHAEL KING</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3474</v>
+        <v>-4.7516</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1731</v>
+        <v>-4.0422</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1743</v>
+        <v>-0.7094</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.4146</v>
+        <v>-2.1679</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6293</v>
+        <v>-2.53</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.7853</v>
+        <v>0.362</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.8164</v>
+        <v>-0.3025</v>
       </c>
       <c r="K25" t="n">
-        <v>0.065</v>
+        <v>-0.3441</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.8814</v>
+        <v>0.0417</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5982</v>
+        <v>-1.8655</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.6943</v>
+        <v>-2.1858</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0961</v>
+        <v>0.3204</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.733</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1833</v>
+        <v>1.2828</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5663</v>
+        <v>-0.2014</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4404</v>
+        <v>-0.0746</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1259</v>
+        <v>-0.1267</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R. SORO VILLANUEVA</t>
+          <t>E. NAVARRO VALDES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.5769</v>
+        <v>-5.1478</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.8719</v>
+        <v>-3.0769</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.705</v>
+        <v>-2.0709</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.0721</v>
+        <v>-3.4146</v>
       </c>
       <c r="H26" t="n">
-        <v>-4.0398</v>
+        <v>-1.6293</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.0323</v>
+        <v>-1.7853</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.9564</v>
+        <v>-1.8164</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.3411</v>
+        <v>0.065</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.6153</v>
+        <v>-1.8814</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.1157</v>
+        <v>-1.5982</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.6987</v>
+        <v>-1.6943</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.417</v>
+        <v>0.0961</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.5498</v>
+        <v>-0.733</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.0158</v>
+        <v>-0.9163</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4661</v>
+        <v>0.1833</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.3667</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.3443</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3215</v>
+        <v>-0.0224</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6231</v>
+        <v>-0.6335</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0.6231</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D. CHALATASHVILI</t>
+          <t>R. SORO VILLANUEVA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.6128</v>
+        <v>-5.1866</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.838</v>
+        <v>-4.3911</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2252</v>
+        <v>-0.7954</v>
       </c>
       <c r="G27" t="n">
-        <v>-4.0513</v>
+        <v>-5.0721</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.4165</v>
+        <v>-4.0398</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.6348</v>
+        <v>-1.0323</v>
       </c>
       <c r="J27" t="n">
-        <v>-3.326</v>
+        <v>-1.9564</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.4029</v>
+        <v>-1.3411</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.9231</v>
+        <v>-0.6153</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-3.1157</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.0136</v>
+        <v>-2.6987</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2882</v>
+        <v>-0.417</v>
       </c>
       <c r="P27" t="n">
         <v>-0.5498</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.8326</v>
+        <v>-2.0158</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6897</v>
+        <v>-0.1878</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.6795</v>
+        <v>-0.4189</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.0103</v>
+        <v>0.2311</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.3219</v>
+        <v>0.6231</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.3219</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.9055</v>
+        <v>-6.1736</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.1379</v>
+        <v>-3.8109</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.7677</v>
+        <v>-2.3626</v>
       </c>
       <c r="G28" t="n">
         <v>-4.069</v>
@@ -2638,13 +2638,13 @@
         <v>1.0995</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.3051</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4744</v>
+        <v>-0.1987</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.7795</v>
+        <v>-0.3744</v>
       </c>
       <c r="V28" t="n">
         <v>0.3011</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-7.6139</v>
+        <v>-8.118</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.0828</v>
+        <v>-6.4674</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.531</v>
+        <v>-1.6506</v>
       </c>
       <c r="G29" t="n">
         <v>-4.9827</v>
@@ -2716,13 +2716,13 @@
         <v>1.4661</v>
       </c>
       <c r="S29" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.4853</v>
       </c>
       <c r="T29" t="n">
-        <v>0.4374</v>
+        <v>0.0528</v>
       </c>
       <c r="U29" t="n">
-        <v>0.552</v>
+        <v>0.4325</v>
       </c>
       <c r="V29" t="n">
         <v>-0.3219</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-40.6033</v>
+        <v>-39.3213</v>
       </c>
       <c r="E30" t="n">
         <v>-30.7955</v>
       </c>
       <c r="F30" t="n">
-        <v>-9.807800000000002</v>
+        <v>-8.525700000000001</v>
       </c>
       <c r="G30" t="n">
         <v>-25.0558</v>
@@ -2767,13 +2767,13 @@
         <v>-7.854500000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.8966</v>
+        <v>-7.896600000000001</v>
       </c>
       <c r="K30" t="n">
         <v>0.9171000000000005</v>
       </c>
       <c r="L30" t="n">
-        <v>-8.813799999999999</v>
+        <v>-8.813800000000001</v>
       </c>
       <c r="M30" t="n">
         <v>-17.1591</v>
@@ -2794,13 +2794,13 @@
         <v>13.7445</v>
       </c>
       <c r="S30" t="n">
-        <v>-1.0104</v>
+        <v>0.2715999999999999</v>
       </c>
       <c r="T30" t="n">
-        <v>-1.0256</v>
+        <v>-1.0255</v>
       </c>
       <c r="U30" t="n">
-        <v>0.01490000000000014</v>
+        <v>1.297</v>
       </c>
       <c r="V30" t="n">
         <v>-3.5413</v>
